--- a/enhancements/test-files/05_Prem_pc0202_2026.xlsx
+++ b/enhancements/test-files/05_Prem_pc0202_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -437,6 +437,13 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -485,6 +492,41 @@
           <t>Trans Eff Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -497,12 +539,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Apex Insurance Brokers</t>
+          <t>Metro Agency Group</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -511,17 +553,42 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2574.81</v>
+        <v>8119.36</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46026</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45967</v>
+        <v>45925</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>46022</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>974.3200000000001</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>496.9</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="P2" t="n">
+        <v>477.42</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -534,12 +601,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -548,16 +615,41 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5489.92</v>
+        <v>15844.71</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46029</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>45997</v>
+        <v>46013</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46025</v>
+        <v>46029</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1901.37</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1140.82</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="P3" t="n">
+        <v>760.55</v>
       </c>
     </row>
     <row r="4">
@@ -571,12 +663,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Global Assurance Corp</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -585,16 +677,41 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7056.05</v>
+        <v>3552.96</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46032</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45871</v>
+        <v>45902</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46032</v>
+        <v>46031</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>426.36</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>294.19</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="P4" t="n">
+        <v>132.17</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +730,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -622,16 +739,41 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5771.49</v>
+        <v>23883.35</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46035</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45934</v>
+        <v>45861</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46034</v>
+        <v>46030</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2866</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1347.02</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0564</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1518.98</v>
       </c>
     </row>
   </sheetData>
@@ -645,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -657,6 +799,13 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,6 +854,41 @@
           <t>Trans Eff Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -717,12 +901,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -731,17 +915,42 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10435.28</v>
+        <v>19567.8</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46060</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>46004</v>
+        <v>45869</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>46058</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>2348.14</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>962.74</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1385.4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -754,12 +963,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -768,17 +977,42 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5107.51</v>
+        <v>13768.87</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46063</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46051</v>
+        <v>45812</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>46061</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1652.26</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>677.4299999999999</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="P3" t="n">
+        <v>974.83</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -791,7 +1025,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,16 +1039,41 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>12610.25</v>
+        <v>18394.66</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45813</v>
+        <v>45882</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46063</v>
+        <v>46065</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>2207.36</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>905.02</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1302.34</v>
       </c>
     </row>
     <row r="5">
@@ -828,12 +1087,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apex Insurance Brokers</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -842,16 +1101,41 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>21673.1</v>
+        <v>20650.1</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46069</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>46055</v>
+        <v>46048</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>46068</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2478.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1709.83</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="P5" t="n">
+        <v>768.1799999999999</v>
       </c>
     </row>
   </sheetData>
@@ -865,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -877,6 +1161,13 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -925,6 +1216,41 @@
           <t>Trans Eff Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -937,12 +1263,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Liberty Mutual</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -951,16 +1277,41 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1324.8</v>
+        <v>15251.2</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46091</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45968</v>
+        <v>45803</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46086</v>
+        <v>46088</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1830.14</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1006.58</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="P2" t="n">
+        <v>823.5599999999999</v>
       </c>
     </row>
     <row r="3">
@@ -974,12 +1325,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -988,16 +1339,41 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11300.09</v>
+        <v>23816.69</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>45974</v>
+        <v>45943</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46093</v>
+        <v>46094</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>2858</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1972.02</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="P3" t="n">
+        <v>885.98</v>
       </c>
     </row>
     <row r="4">
@@ -1011,12 +1387,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Global Assurance Corp</t>
+          <t>Liberty Mutual</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1025,16 +1401,41 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10813.95</v>
+        <v>10609.26</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45926</v>
+        <v>45823</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46097</v>
+        <v>46093</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1273.11</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>560.17</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="P4" t="n">
+        <v>712.9400000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1048,12 +1449,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1062,16 +1463,41 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>21870.21</v>
+        <v>8314.57</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46100</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45938</v>
+        <v>46001</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46099</v>
+        <v>46095</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>997.75</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>458.97</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="P5" t="n">
+        <v>538.78</v>
       </c>
     </row>
   </sheetData>
@@ -1085,7 +1511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1097,6 +1523,13 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1145,6 +1578,41 @@
           <t>Trans Eff Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1157,12 +1625,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Global Assurance Corp</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1171,16 +1639,41 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4053.02</v>
+        <v>19163.97</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45946</v>
+        <v>45991</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46120</v>
+        <v>46123</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>2299.68</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1517.79</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="P2" t="n">
+        <v>781.89</v>
       </c>
     </row>
     <row r="3">
@@ -1194,7 +1687,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1208,16 +1701,41 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>14997.7</v>
+        <v>15595.67</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>45995</v>
+        <v>46072</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46127</v>
+        <v>46123</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1871.48</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1141.6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0732</v>
+      </c>
+      <c r="P3" t="n">
+        <v>729.88</v>
       </c>
     </row>
     <row r="4">
@@ -1245,16 +1763,41 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3807.2</v>
+        <v>14047.69</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46131</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>46034</v>
+        <v>46083</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46126</v>
+        <v>46129</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1685.72</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>809.15</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0576</v>
+      </c>
+      <c r="P4" t="n">
+        <v>876.5700000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1282,16 +1825,41 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>24422.88</v>
+        <v>1709.87</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45965</v>
+        <v>46056</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46129</v>
+        <v>46133</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>205.18</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>116.95</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="P5" t="n">
+        <v>88.23</v>
       </c>
     </row>
   </sheetData>
@@ -1305,7 +1873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1317,6 +1885,13 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1365,6 +1940,41 @@
           <t>Trans Eff Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1377,12 +1987,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Global Assurance Corp</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1391,17 +2001,42 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3091.54</v>
+        <v>7291.06</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45944</v>
+        <v>45878</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>46154</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>874.9299999999999</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>524.96</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="P2" t="n">
+        <v>349.97</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1414,12 +2049,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Global Assurance Corp</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Apex Insurance Brokers</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1428,17 +2063,42 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13307.59</v>
+        <v>19784.78</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46076</v>
+        <v>46124</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>46160</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>2374.17</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1092.12</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1282.05</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1451,12 +2111,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1465,16 +2125,41 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1147.06</v>
+        <v>21993.9</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46164</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>46068</v>
+        <v>46048</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46163</v>
+        <v>46159</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>2639.27</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1398.81</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0636</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1240.46</v>
       </c>
     </row>
     <row r="5">
@@ -1488,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Liberty Mutual</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Metro Agency Group</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1502,16 +2187,41 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>9590.610000000001</v>
+        <v>11919.17</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46167</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45967</v>
+        <v>45999</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46167</v>
+        <v>46166</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1430.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>715.15</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P5" t="n">
+        <v>715.15</v>
       </c>
     </row>
   </sheetData>
@@ -1525,7 +2235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1537,6 +2247,13 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1585,6 +2302,41 @@
           <t>Trans Eff Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1597,7 +2349,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1611,16 +2363,41 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>17491.42</v>
+        <v>9912.309999999999</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>46008</v>
+        <v>46169</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46187</v>
+        <v>46188</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1189.48</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>606.63</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="P2" t="n">
+        <v>582.85</v>
       </c>
     </row>
     <row r="3">
@@ -1634,7 +2411,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1648,16 +2425,41 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5188.81</v>
+        <v>21744.38</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46195</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46008</v>
+        <v>45985</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46191</v>
+        <v>46193</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>2609.33</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1200.29</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1409.04</v>
       </c>
     </row>
     <row r="4">
@@ -1676,7 +2478,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1685,16 +2487,41 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>16932.5</v>
+        <v>8805.700000000001</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46198</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>46030</v>
+        <v>46080</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46194</v>
+        <v>46196</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1056.68</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>644.5700000000001</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0732</v>
+      </c>
+      <c r="P4" t="n">
+        <v>412.11</v>
       </c>
     </row>
     <row r="5">
@@ -1708,12 +2535,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Liberty Mutual</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1722,16 +2549,41 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4445.48</v>
+        <v>4758.99</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>46052</v>
+        <v>46076</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46169</v>
+        <v>46174</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>571.08</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>296.96</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="P5" t="n">
+        <v>274.12</v>
       </c>
     </row>
   </sheetData>
